--- a/data/trans_orig/IP16_n_R2-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16_n_R2-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2712</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7796</t>
+          <t>8001</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2267</t>
+          <t>2232</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7940</t>
+          <t>8520</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14430</t>
+          <t>14162</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3667</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>8956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9373</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17398</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,5%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>9973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5336</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12271</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11012</t>
+          <t>10978</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20255</t>
+          <t>20203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>55,22%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6651</t>
+          <t>6757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12938</t>
+          <t>13035</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7585</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14541</t>
+          <t>14520</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16331</t>
+          <t>16383</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25574</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,99%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7953</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5580</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,84%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11472</t>
+          <t>11727</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9337</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5564</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9930</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17512</t>
+          <t>17991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>81,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8981</t>
+          <t>9242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10909</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20676</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7370</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13376</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>59,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21868</t>
+          <t>21528</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1459</t>
+          <t>1625</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6531</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>727</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4690</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>59,97%</t>
+          <t>67,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3102</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9913</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>58,49%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>7501</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13720</t>
+          <t>13845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,7%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3452</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9000</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8850</t>
+          <t>9444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9213</t>
+          <t>8982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16398</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>72,07%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3379</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8927</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13895</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14970</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21674</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12377</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11556</t>
+          <t>11772</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>19715</t>
+          <t>19775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26351</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37530</t>
+          <t>36991</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,02%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5631</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13768</t>
+          <t>13471</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7059</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>16141</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>14831</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27213</t>
+          <t>26478</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>12453</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20293</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23954</t>
+          <t>23726</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32808</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38577</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>50959</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>77,36%</t>
+          <t>77,46%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>39093</t>
+          <t>39714</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56965</t>
+          <t>57125</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>47798</t>
+          <t>48140</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>65808</t>
+          <t>66271</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>93218</t>
+          <t>92190</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>118258</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>43,93%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68180</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>86212</t>
+          <t>85591</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>78111</t>
+          <t>77648</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>96121</t>
+          <t>95779</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>150966</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>176006</t>
+          <t>177034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,76%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2792</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>6437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4673</t>
+          <t>4659</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>39,14%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6432</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13300</t>
+          <t>13056</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12946</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18631</t>
+          <t>17982</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21464</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30050</t>
+          <t>30064</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>60,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,58%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>937</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6543</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8508</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16940</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>22546</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19875</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39951</t>
+          <t>39770</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46289</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>96,04%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2072</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>8848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4828</t>
+          <t>4248</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>34,03%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8569</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13461</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24728</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>33591</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,66%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6281</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13396</t>
+          <t>13414</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18461</t>
+          <t>18664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8961</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14566</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24476</t>
+          <t>25449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32339</t>
+          <t>32311</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,49%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7190</t>
+          <t>7083</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>635</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4737</t>
+          <t>4730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9637</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,03%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,44%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7550</t>
+          <t>7557</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17158</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>24451</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5186</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3805</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6678</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,96%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10499</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>14368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22668</t>
+          <t>22403</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>28328</t>
+          <t>28321</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1775</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>8579</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>652</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5026</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3254</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11372</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24927</t>
+          <t>24784</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20295</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24707</t>
+          <t>24693</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>48508</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5117</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2414</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9726</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>29,4%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16106</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20659</t>
+          <t>20653</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11966</t>
+          <t>12337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19278</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30429</t>
+          <t>30298</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39334</t>
+          <t>39249</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,91%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,46%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19656</t>
+          <t>18904</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>35575</t>
+          <t>35340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15011</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29427</t>
+          <t>30154</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36973</t>
+          <t>37709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59728</t>
+          <t>60077</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>112361</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128045</t>
+          <t>128797</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>129147</t>
+          <t>128420</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143563</t>
+          <t>143251</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>80,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>246546</t>
+          <t>246197</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>269301</t>
+          <t>268565</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,69%</t>
         </is>
       </c>
     </row>
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6183</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>770</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13023</t>
+          <t>12863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18416</t>
+          <t>18431</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29013</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6581</t>
+          <t>6910</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14898</t>
+          <t>15324</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,96%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20682</t>
+          <t>20353</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26627</t>
+          <t>26265</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10487</t>
+          <t>10214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16914</t>
+          <t>16801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33047</t>
+          <t>32621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>42446</t>
+          <t>42333</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4229</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,76%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13700</t>
+          <t>13619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>9268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5215</t>
+          <t>5419</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>12198</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14674</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21043</t>
+          <t>21108</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20365</t>
+          <t>20161</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24961</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>37181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>45200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3388</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,2%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>550</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4666</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>39,95%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5165</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>4097</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12149</t>
+          <t>12231</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1254</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>6683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3300</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2271</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12902</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,88%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>16680</t>
+          <t>16117</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>22583</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>517</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4473</t>
+          <t>4406</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4781</t>
+          <t>5441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1246</t>
+          <t>1640</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7271</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20411</t>
+          <t>20402</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20231</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>24432</t>
+          <t>24424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>38660</t>
+          <t>38521</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44685</t>
+          <t>44291</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11295</t>
+          <t>10393</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>22664</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11485</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>24391</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25228</t>
+          <t>25200</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>42264</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104533</t>
+          <t>104797</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>117068</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>99141</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111589</t>
+          <t>111791</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>207705</t>
+          <t>208473</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>225509</t>
+          <t>225537</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>6613</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>441</t>
+          <t>451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9848</t>
+          <t>10822</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23951</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29764</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14905</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21881</t>
+          <t>21871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42858</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50785</t>
+          <t>50418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,66%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11113</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>22023</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13054</t>
+          <t>13706</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44397</t>
+          <t>45203</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34774</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>59053</t>
+          <t>58604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>25490</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>37050</t>
+          <t>36712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,92%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>76,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>66820</t>
+          <t>66014</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>98163</t>
+          <t>97511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,08%</t>
+          <t>59,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>87,68%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2556</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8232</t>
+          <t>8559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>9305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,51%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15553</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9709</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,11%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11055</t>
+          <t>10982</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18192</t>
+          <t>18002</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23110</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32233</t>
+          <t>31809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>59,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1742</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8194</t>
+          <t>8163</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13949</t>
+          <t>14008</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10779</t>
+          <t>10793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2910</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9644</t>
+          <t>9585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18426</t>
+          <t>18425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6314</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>825</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5465</t>
+          <t>5442</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>3979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10568</t>
+          <t>10709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1923</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>5247</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9864</t>
+          <t>9740</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>8217</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>78,98%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2888</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>37,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3370</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>3753</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,2%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10358</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17525</t>
+          <t>17534</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,37%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10805</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>19835</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9946</t>
+          <t>10237</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23522</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>51,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>23073</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40519</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>54,15%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9951</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>18959</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20832</t>
+          <t>21406</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34408</t>
+          <t>34117</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33621</t>
+          <t>33990</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>50184</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,88%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>80,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9844</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>14754</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>74,44%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6054</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7580</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5021</t>
+          <t>5065</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>12381</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,47%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29750</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65193</t>
+          <t>64467</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>50027</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73332</t>
+          <t>72760</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>86563</t>
+          <t>85984</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129050</t>
+          <t>130359</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,22%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>112522</t>
+          <t>113248</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>147965</t>
+          <t>147134</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>108869</t>
+          <t>109441</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132249</t>
+          <t>132174</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>230866</t>
+          <t>229557</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>273353</t>
+          <t>273932</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,11%</t>
         </is>
       </c>
     </row>
